--- a/测试用例-D1-用户详情接口.xlsx
+++ b/测试用例-D1-用户详情接口.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$3:$K$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
     <row r="2" ht="17" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>缺陷：查询不存在的用户时返回 Java 异常信息，泄露包名/类名/方法名 ｜ 用例 10 条（通过 5 / 失败 5）</t>
+          <t>用例 10 条（通过 5 / 失败 5）</t>
         </is>
       </c>
     </row>
@@ -585,21 +585,11 @@
           <t>状态</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>关联缺陷</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="4" ht="44.5" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-DTL-001</t>
+          <t>TC-001</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -653,17 +643,11 @@
           <t>通过</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>基准用例，用于对照</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-DTL-002</t>
+          <t>TC-002</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -719,21 +703,11 @@
           <t>失败</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>核心缺陷用例：泄露包名/类名/方法名</t>
-        </is>
-      </c>
     </row>
     <row r="6" ht="44.5" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-DTL-003</t>
+          <t>TC-003</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -773,7 +747,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>同 TC-USER-DTL-002：应返回可读提示，不泄露内部信息</t>
+          <t>同 TC-002：应返回可读提示，不泄露内部信息</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -784,23 +758,13 @@
       <c r="K6" s="7" t="inlineStr">
         <is>
           <t>失败</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>证明与具体取值无关，属通用判空缺失</t>
         </is>
       </c>
     </row>
     <row r="7" ht="44.5" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-DTL-004</t>
+          <t>TC-004</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -851,23 +815,13 @@
       <c r="K7" s="7" t="inlineStr">
         <is>
           <t>失败</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>提示本身可读，但暴露了内部类型名 java.lang.Long</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-DTL-005</t>
+          <t>TC-005</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -921,21 +875,11 @@
           <t>失败</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>Long 类型上界；同样触发判空缺失，与 TC-002 同根因</t>
-        </is>
-      </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-DTL-006</t>
+          <t>TC-006</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -989,21 +933,11 @@
           <t>失败</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>0 值同样触发判空缺失，说明任何查不到的值都会 NPE</t>
-        </is>
-      </c>
     </row>
     <row r="10" ht="44.5" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-DTL-007</t>
+          <t>TC-007</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1054,19 +988,13 @@
       <c r="K10" s="6" t="inlineStr">
         <is>
           <t>通过</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>走 {"/"} 无参分支，行为正常，未报内部异常</t>
         </is>
       </c>
     </row>
     <row r="11" ht="31" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-DTL-008</t>
+          <t>TC-008</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1121,17 +1049,11 @@
           <t>通过</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>鉴权拦截生效，提示可读</t>
-        </is>
-      </c>
     </row>
     <row r="12" ht="31" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-DTL-009</t>
+          <t>TC-009</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1185,17 +1107,11 @@
           <t>通过</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>数据范围校验给出了可读提示，可作为 D1 预期的对照依据</t>
-        </is>
-      </c>
     </row>
     <row r="13" ht="31" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>TC-USER-DTL-010</t>
+          <t>TC-010</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1248,18 +1164,12 @@
           <t>通过</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>数据范围内可正常访问</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M13"/>
+  <autoFilter ref="A3:K13"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1271,7 +1181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1305,253 +1215,213 @@
     <row r="3" ht="17.5" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>关联缺陷</t>
+          <t>用例总数</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>D1 —— 查询不存在的用户时返回 Java 异常信息，泄露包名/类名/方法名</t>
+          <t>10 条（通过 5 / 失败 5）</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17.5" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>用例总数</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>10 条（通过 5 / 失败 5）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.5" customHeight="1">
-      <c r="A5" s="9" t="inlineStr"/>
-      <c r="B5" s="10" t="inlineStr"/>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr"/>
+      <c r="B4" s="10" t="inlineStr"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>字段说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17.5" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>用例编号</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>TC-序号，同一文件内唯一</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17.5" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>用例编号</t>
+          <t>优先级</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>TC-模块-序号，同一文件内唯一</t>
+          <t>P0 核心必测 / P1 重要 / P2 一般</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17.5" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>优先级</t>
+          <t>用例类型</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>P0 核心必测 / P1 重要 / P2 一般</t>
+          <t>功能 / 边界 / 异常 / 安全 / 权限 / 组合 / 对照 / 回归</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17.5" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>用例类型</t>
+          <t>前置条件</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>功能 / 边界 / 异常 / 安全 / 权限 / 组合 / 回归</t>
+          <t>执行该用例前必须满足的状态</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17.5" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>前置条件</t>
+          <t>测试步骤</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>执行该用例前必须满足的状态</t>
+          <t>可被他人在相同环境照着重现的操作</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17.5" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>测试步骤</t>
+          <t>测试数据</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>可被他人在相同环境照着重现的操作</t>
+          <t>本条用例使用的具体参数值</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17.5" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>测试数据</t>
+          <t>预期结果</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>本条用例使用的具体参数值</t>
+          <t>执行之前写下的、功能正确时应有的表现</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17.5" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>预期结果</t>
+          <t>实际结果</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>执行之前写下的、功能正确时应有的表现</t>
+          <t>执行之后记录的真实响应</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17.5" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>实际结果</t>
+          <t>状态</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>执行之后记录的真实响应</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="17.5" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
           <t>通过 / 失败 / 待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>状态含义</t>
         </is>
       </c>
     </row>
     <row r="16" ht="17.5" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>关联缺陷</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>对应的缺陷编号，便于追溯</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>状态含义</t>
+          <t>实际结果与预期一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="17.5" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>预期结果未被满足，即接口行为不符合预期（不是用例写错了）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="17.5" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>待执行</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>实际结果与预期一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="17.5" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>预期结果未被满足，即接口行为不符合预期，已提交缺陷报告（不是用例写错了）</t>
+          <t>测试环境服务未启动，尚未执行，实际结果留空</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>执行情况</t>
         </is>
       </c>
     </row>
     <row r="20" ht="17.5" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>待执行</t>
+          <t>执行状态</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>测试环境服务未启动，尚未执行，实际结果留空</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>执行情况</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="17.5" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>执行状态</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
           <t>全部 10 条用例已执行完毕，无未执行项。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="17.5" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="21" ht="17.5" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>证据</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>失败用例的截图见仓库 证据/ 目录，文件名以缺陷编号开头（如 D1-01-请求与响应.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="17.5" customHeight="1">
-      <c r="A24" s="9" t="inlineStr"/>
-      <c r="B24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="17.5" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>TC-005（超大值）与 TC-006（0 值）同样触发 NPE，说明该接口对任何查不到的 userId 都未做判空。</t>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>失败用例的截图见仓库 证据/ 目录（D1-01-请求与响应.png）</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
